--- a/config.xlsx
+++ b/config.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ithiroshima.sharepoint.com/sites/msteams_b591de-/Shared Documents/重要資料/00000000_作業領域/Git/image_draw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_5AD1236956A4005EAD7F99C3BD3B0BFE2422EEF3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E8A095C-C23F-4E51-BABF-2C7FF00DE6CC}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="11_5AD1236956A4005EAD7F99C3BD3B0BFE2422EEF3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F985AA3-679A-4335-9E6F-FA2D9A7D089A}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2010" yWindow="2670" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
   <si>
     <t>key</t>
   </si>
@@ -141,12 +150,6 @@
     <t>円および文字の線幅</t>
   </si>
   <si>
-    <t>trigger_fpga_time</t>
-  </si>
-  <si>
-    <t>トリガ用IP反応時間[sec]（手動確認値）</t>
-  </si>
-  <si>
     <t>sync_mode</t>
   </si>
   <si>
@@ -166,10 +169,6 @@
   </si>
   <si>
     <t>F:\temp\20260217_高速度カメラ\018\018.txt</t>
-  </si>
-  <si>
-    <t>frame_01234.jpg</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>jpg</t>
@@ -180,6 +179,40 @@
   </si>
   <si>
     <t>入力画像拡張子</t>
+  </si>
+  <si>
+    <t>mm_to_px_ax</t>
+  </si>
+  <si>
+    <t>x方向スケール [px/mm]</t>
+  </si>
+  <si>
+    <t>mm_to_px_ay</t>
+  </si>
+  <si>
+    <t>y方向スケール [px/mm]</t>
+  </si>
+  <si>
+    <t>mm_to_px_bx</t>
+  </si>
+  <si>
+    <t>x方向オフセット [px]</t>
+  </si>
+  <si>
+    <t>mm_to_px_by</t>
+  </si>
+  <si>
+    <t>y方向オフセット [px]</t>
+  </si>
+  <si>
+    <t>Img000020.jpg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>trigger_fpga_count</t>
+  </si>
+  <si>
+    <t>トリガIP反応FPGAカウント</t>
   </si>
 </sst>
 </file>
@@ -222,8 +255,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -504,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
@@ -528,7 +562,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>20000</v>
+        <v>450000</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -538,7 +572,7 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>150000000</v>
       </c>
       <c r="C3" t="s">
@@ -547,13 +581,13 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B4">
-        <v>0.82345599999999997</v>
+        <v>482</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -561,7 +595,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -569,24 +603,24 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" t="s">
-        <v>47</v>
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -594,7 +628,7 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>3000</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -605,7 +639,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -616,7 +650,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
@@ -627,7 +661,7 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -638,7 +672,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -649,7 +683,7 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
@@ -723,13 +757,57 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21">
+        <v>5.3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22">
+        <v>5.3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ithiroshima.sharepoint.com/sites/msteams_b591de-/Shared Documents/重要資料/00000000_作業領域/Git/image_draw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_5AD1236956A4005EAD7F99C3BD3B0BFE2422EEF3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F985AA3-679A-4335-9E6F-FA2D9A7D089A}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="11_5AD1236956A4005EAD7F99C3BD3B0BFE2422EEF3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB86A52-80BA-49B4-8346-890AF580553C}"/>
   <bookViews>
-    <workbookView xWindow="2010" yWindow="2670" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>key</t>
   </si>
@@ -90,9 +90,6 @@
     <t>FPGAログファイル</t>
   </si>
   <si>
-    <t>ip_position_csv</t>
-  </si>
-  <si>
     <t>IP位置情報CSV</t>
   </si>
   <si>
@@ -157,12 +154,6 @@
   </si>
   <si>
     <t>同期方式（trigger固定）</t>
-  </si>
-  <si>
-    <t>F:\temp\20260217_高速度カメラ\018\Test1\018</t>
-  </si>
-  <si>
-    <t>F:\temp\20260217_高速度カメラ\018\Test1\018_out</t>
   </si>
   <si>
     <t>C:\Users\yatsu\OneDrive - HIT\00000000_作業領域\Git\image_draw\IP_position_32ch_w_press.csv</t>
@@ -213,6 +204,22 @@
   </si>
   <si>
     <t>トリガIP反応FPGAカウント</t>
+  </si>
+  <si>
+    <t>ip_position_csv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F:\temp\20260217_高速度カメラ\018\02\Test1\018</t>
+  </si>
+  <si>
+    <t>F:\temp\20260217_高速度カメラ\018\02\Test1\018_out</t>
+  </si>
+  <si>
+    <t>draw_scale</t>
+  </si>
+  <si>
+    <t>描画用拡大倍率</t>
   </si>
 </sst>
 </file>
@@ -538,15 +545,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -557,7 +564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -568,51 +575,54 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>150000000</v>
+        <v>148000000</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="1">
+        <v>150000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>482</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -622,192 +632,209 @@
       <c r="C7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>49</v>
+        <v>1019</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="C13" t="s">
         <v>21</v>
       </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
         <v>23</v>
       </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>25</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>26</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>28</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
         <v>31</v>
-      </c>
-      <c r="B17" t="b">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18">
         <v>0.5</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B21">
-        <v>5.3</v>
+        <v>5.05</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B22">
-        <v>5.3</v>
+        <v>5.05</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B23">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B24">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -818,6 +845,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="983f7082-b7eb-4457-b011-7049091eb845">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100E842C2E132CE1C49AF060988EAB5D878" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="4100fd7ecd3ab7bde23f2adf575325e1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="983f7082-b7eb-4457-b011-7049091eb845" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e41944d2d023fa419fe74fd72a7c768" ns2:_="">
     <xsd:import namespace="983f7082-b7eb-4457-b011-7049091eb845"/>
@@ -1007,16 +1044,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="983f7082-b7eb-4457-b011-7049091eb845">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1027,6 +1054,16 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B1E5F6E-1B81-4F76-809D-90AA1538033C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="983f7082-b7eb-4457-b011-7049091eb845"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C1ED949-74E9-4400-B66B-E10A113D8C76}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1044,16 +1081,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B1E5F6E-1B81-4F76-809D-90AA1538033C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="983f7082-b7eb-4457-b011-7049091eb845"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C0CCECB-52BA-4D05-B33B-42A827BED451}">
   <ds:schemaRefs>
